--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252126</v>
+        <v>121252127</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R2" t="n">
-        <v>7241938</v>
+        <v>7241880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252130</v>
+        <v>121252124</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>89753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,16 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>757</v>
+        <v>1962</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781562</v>
+        <v>781534</v>
       </c>
       <c r="R3" t="n">
-        <v>7241723</v>
+        <v>7241742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -876,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252127</v>
+        <v>121252128</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,7 +922,7 @@
         <v>781534</v>
       </c>
       <c r="R4" t="n">
-        <v>7241880</v>
+        <v>7241742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252124</v>
+        <v>121252123</v>
       </c>
       <c r="B5" t="n">
-        <v>89743</v>
+        <v>90623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781534</v>
+        <v>781648</v>
       </c>
       <c r="R5" t="n">
-        <v>7241742</v>
+        <v>7241716</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252128</v>
+        <v>121252125</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1092,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781534</v>
+        <v>781581</v>
       </c>
       <c r="R6" t="n">
-        <v>7241742</v>
+        <v>7241728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252125</v>
+        <v>121252126</v>
       </c>
       <c r="B7" t="n">
-        <v>78335</v>
+        <v>92008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781581</v>
+        <v>781593</v>
       </c>
       <c r="R7" t="n">
-        <v>7241728</v>
+        <v>7241938</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1284,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252123</v>
+        <v>121252130</v>
       </c>
       <c r="B8" t="n">
-        <v>90613</v>
+        <v>91388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,21 +1304,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781648</v>
+        <v>781562</v>
       </c>
       <c r="R8" t="n">
-        <v>7241716</v>
+        <v>7241723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>121252129</v>
       </c>
       <c r="B9" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252127</v>
+        <v>121252129</v>
       </c>
       <c r="B2" t="n">
         <v>91973</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781534</v>
+        <v>781569</v>
       </c>
       <c r="R2" t="n">
-        <v>7241880</v>
+        <v>7241747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252128</v>
+        <v>121252127</v>
       </c>
       <c r="B4" t="n">
         <v>91973</v>
@@ -922,7 +922,7 @@
         <v>781534</v>
       </c>
       <c r="R4" t="n">
-        <v>7241742</v>
+        <v>7241880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252123</v>
+        <v>121252126</v>
       </c>
       <c r="B5" t="n">
-        <v>90623</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781648</v>
+        <v>781593</v>
       </c>
       <c r="R5" t="n">
-        <v>7241716</v>
+        <v>7241938</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1065,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252125</v>
+        <v>121252128</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781581</v>
+        <v>781534</v>
       </c>
       <c r="R6" t="n">
-        <v>7241728</v>
+        <v>7241742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252126</v>
+        <v>121252130</v>
       </c>
       <c r="B7" t="n">
-        <v>92008</v>
+        <v>91388</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1202,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781593</v>
+        <v>781562</v>
       </c>
       <c r="R7" t="n">
-        <v>7241938</v>
+        <v>7241723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252130</v>
+        <v>121252125</v>
       </c>
       <c r="B8" t="n">
-        <v>91388</v>
+        <v>78338</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,16 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>757</v>
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781562</v>
+        <v>781581</v>
       </c>
       <c r="R8" t="n">
-        <v>7241723</v>
+        <v>7241728</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252129</v>
+        <v>121252123</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>90623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781569</v>
+        <v>781648</v>
       </c>
       <c r="R9" t="n">
-        <v>7241747</v>
+        <v>7241716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252129</v>
+        <v>121252123</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>90635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781569</v>
+        <v>781648</v>
       </c>
       <c r="R2" t="n">
-        <v>7241747</v>
+        <v>7241716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252124</v>
+        <v>121252127</v>
       </c>
       <c r="B3" t="n">
-        <v>89753</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +820,7 @@
         <v>781534</v>
       </c>
       <c r="R3" t="n">
-        <v>7241742</v>
+        <v>7241880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252127</v>
+        <v>121252130</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781534</v>
+        <v>781562</v>
       </c>
       <c r="R4" t="n">
-        <v>7241880</v>
+        <v>7241723</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +958,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252126</v>
+        <v>121252124</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>89760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R5" t="n">
-        <v>7241938</v>
+        <v>7241742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1061,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252128</v>
+        <v>121252129</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781534</v>
+        <v>781569</v>
       </c>
       <c r="R6" t="n">
-        <v>7241742</v>
+        <v>7241747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252130</v>
+        <v>121252125</v>
       </c>
       <c r="B7" t="n">
-        <v>91388</v>
+        <v>78341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,16 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>757</v>
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781562</v>
+        <v>781581</v>
       </c>
       <c r="R7" t="n">
-        <v>7241723</v>
+        <v>7241728</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1284,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252125</v>
+        <v>121252126</v>
       </c>
       <c r="B8" t="n">
-        <v>78338</v>
+        <v>92020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,21 +1299,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781581</v>
+        <v>781593</v>
       </c>
       <c r="R8" t="n">
-        <v>7241728</v>
+        <v>7241938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252123</v>
+        <v>121252128</v>
       </c>
       <c r="B9" t="n">
-        <v>90623</v>
+        <v>91985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781648</v>
+        <v>781534</v>
       </c>
       <c r="R9" t="n">
-        <v>7241716</v>
+        <v>7241742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252123</v>
+        <v>121252125</v>
       </c>
       <c r="B2" t="n">
-        <v>90635</v>
+        <v>78341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781648</v>
+        <v>781581</v>
       </c>
       <c r="R2" t="n">
-        <v>7241716</v>
+        <v>7241728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252127</v>
+        <v>121252129</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781534</v>
+        <v>781569</v>
       </c>
       <c r="R3" t="n">
-        <v>7241880</v>
+        <v>7241747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252130</v>
+        <v>121252126</v>
       </c>
       <c r="B4" t="n">
-        <v>91400</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>757</v>
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781562</v>
+        <v>781593</v>
       </c>
       <c r="R4" t="n">
-        <v>7241723</v>
+        <v>7241938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252124</v>
+        <v>121252130</v>
       </c>
       <c r="B5" t="n">
-        <v>89760</v>
+        <v>91401</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,21 +998,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781534</v>
+        <v>781562</v>
       </c>
       <c r="R5" t="n">
-        <v>7241742</v>
+        <v>7241723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1079,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252129</v>
+        <v>121252128</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781569</v>
+        <v>781534</v>
       </c>
       <c r="R6" t="n">
-        <v>7241747</v>
+        <v>7241742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252125</v>
+        <v>121252123</v>
       </c>
       <c r="B7" t="n">
-        <v>78341</v>
+        <v>90636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781581</v>
+        <v>781648</v>
       </c>
       <c r="R7" t="n">
-        <v>7241728</v>
+        <v>7241716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252126</v>
+        <v>121252124</v>
       </c>
       <c r="B8" t="n">
-        <v>92020</v>
+        <v>89761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R8" t="n">
-        <v>7241938</v>
+        <v>7241742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252128</v>
+        <v>121252127</v>
       </c>
       <c r="B9" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>781534</v>
       </c>
       <c r="R9" t="n">
-        <v>7241742</v>
+        <v>7241880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252125</v>
       </c>
       <c r="B2" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252129</v>
+        <v>121252127</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781569</v>
+        <v>781534</v>
       </c>
       <c r="R3" t="n">
-        <v>7241747</v>
+        <v>7241880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252126</v>
+        <v>121252128</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R4" t="n">
-        <v>7241938</v>
+        <v>7241742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252130</v>
+        <v>121252126</v>
       </c>
       <c r="B5" t="n">
-        <v>91401</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,16 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>757</v>
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781562</v>
+        <v>781593</v>
       </c>
       <c r="R5" t="n">
-        <v>7241723</v>
+        <v>7241938</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252128</v>
+        <v>121252124</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>89764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1092,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252123</v>
+        <v>121252129</v>
       </c>
       <c r="B7" t="n">
-        <v>90636</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1194,25 +1198,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781648</v>
+        <v>781569</v>
       </c>
       <c r="R7" t="n">
-        <v>7241716</v>
+        <v>7241747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252124</v>
+        <v>121252123</v>
       </c>
       <c r="B8" t="n">
-        <v>89761</v>
+        <v>90639</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781534</v>
+        <v>781648</v>
       </c>
       <c r="R8" t="n">
-        <v>7241742</v>
+        <v>7241716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252127</v>
+        <v>121252130</v>
       </c>
       <c r="B9" t="n">
-        <v>91986</v>
+        <v>91404</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,25 +1402,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781534</v>
+        <v>781562</v>
       </c>
       <c r="R9" t="n">
-        <v>7241880</v>
+        <v>7241723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1469,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252125</v>
+        <v>121252127</v>
       </c>
       <c r="B2" t="n">
-        <v>78344</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781581</v>
+        <v>781534</v>
       </c>
       <c r="R2" t="n">
-        <v>7241728</v>
+        <v>7241880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252127</v>
+        <v>121252128</v>
       </c>
       <c r="B3" t="n">
         <v>91989</v>
@@ -820,7 +820,7 @@
         <v>781534</v>
       </c>
       <c r="R3" t="n">
-        <v>7241880</v>
+        <v>7241742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252128</v>
+        <v>121252125</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781534</v>
+        <v>781581</v>
       </c>
       <c r="R4" t="n">
-        <v>7241742</v>
+        <v>7241728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252126</v>
+        <v>121252123</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>90639</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781593</v>
+        <v>781648</v>
       </c>
       <c r="R5" t="n">
-        <v>7241938</v>
+        <v>7241716</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252124</v>
+        <v>121252129</v>
       </c>
       <c r="B6" t="n">
-        <v>89764</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1096,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781534</v>
+        <v>781569</v>
       </c>
       <c r="R6" t="n">
-        <v>7241742</v>
+        <v>7241747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252129</v>
+        <v>121252126</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>92024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781569</v>
+        <v>781593</v>
       </c>
       <c r="R7" t="n">
-        <v>7241747</v>
+        <v>7241938</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252123</v>
+        <v>121252130</v>
       </c>
       <c r="B8" t="n">
-        <v>90639</v>
+        <v>91404</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,21 +1304,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781648</v>
+        <v>781562</v>
       </c>
       <c r="R8" t="n">
-        <v>7241716</v>
+        <v>7241723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252130</v>
+        <v>121252124</v>
       </c>
       <c r="B9" t="n">
-        <v>91404</v>
+        <v>89764</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,16 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>757</v>
+        <v>1962</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781562</v>
+        <v>781534</v>
       </c>
       <c r="R9" t="n">
-        <v>7241723</v>
+        <v>7241742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1470,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252127</v>
+        <v>121252128</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>781534</v>
       </c>
       <c r="R2" t="n">
-        <v>7241880</v>
+        <v>7241742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252128</v>
+        <v>121252123</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>90645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781534</v>
+        <v>781648</v>
       </c>
       <c r="R3" t="n">
-        <v>7241742</v>
+        <v>7241716</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252125</v>
+        <v>121252130</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>91410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781581</v>
+        <v>781562</v>
       </c>
       <c r="R4" t="n">
-        <v>7241728</v>
+        <v>7241723</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +958,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252123</v>
+        <v>121252125</v>
       </c>
       <c r="B5" t="n">
-        <v>90639</v>
+        <v>78345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781648</v>
+        <v>781581</v>
       </c>
       <c r="R5" t="n">
-        <v>7241716</v>
+        <v>7241728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252129</v>
+        <v>121252124</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>89768</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1091,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781569</v>
+        <v>781534</v>
       </c>
       <c r="R6" t="n">
-        <v>7241747</v>
+        <v>7241742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252126</v>
+        <v>121252129</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>91995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1193,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781593</v>
+        <v>781569</v>
       </c>
       <c r="R7" t="n">
-        <v>7241938</v>
+        <v>7241747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1265,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252130</v>
+        <v>121252127</v>
       </c>
       <c r="B8" t="n">
-        <v>91404</v>
+        <v>91995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,20 +1295,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>757</v>
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781562</v>
+        <v>781534</v>
       </c>
       <c r="R8" t="n">
-        <v>7241723</v>
+        <v>7241880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252124</v>
+        <v>121252126</v>
       </c>
       <c r="B9" t="n">
-        <v>89764</v>
+        <v>92030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781534</v>
+        <v>781593</v>
       </c>
       <c r="R9" t="n">
-        <v>7241742</v>
+        <v>7241938</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1469,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252128</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252123</v>
+        <v>121252130</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
+        <v>91411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781648</v>
+        <v>781562</v>
       </c>
       <c r="R3" t="n">
-        <v>7241716</v>
+        <v>7241723</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +856,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252130</v>
+        <v>121252125</v>
       </c>
       <c r="B4" t="n">
-        <v>91410</v>
+        <v>78346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +891,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>757</v>
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781562</v>
+        <v>781581</v>
       </c>
       <c r="R4" t="n">
-        <v>7241723</v>
+        <v>7241728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,7 +959,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252125</v>
+        <v>121252124</v>
       </c>
       <c r="B5" t="n">
-        <v>78345</v>
+        <v>89769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781581</v>
+        <v>781534</v>
       </c>
       <c r="R5" t="n">
-        <v>7241728</v>
+        <v>7241742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252124</v>
+        <v>121252126</v>
       </c>
       <c r="B6" t="n">
-        <v>89768</v>
+        <v>92031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781534</v>
+        <v>781593</v>
       </c>
       <c r="R6" t="n">
-        <v>7241742</v>
+        <v>7241938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,6 +1163,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>121252129</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,7 +1287,7 @@
         <v>121252127</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252126</v>
+        <v>121252123</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>90646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781593</v>
+        <v>781648</v>
       </c>
       <c r="R9" t="n">
-        <v>7241938</v>
+        <v>7241716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1470,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252128</v>
+        <v>121252123</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>90646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781534</v>
+        <v>781648</v>
       </c>
       <c r="R2" t="n">
-        <v>7241742</v>
+        <v>7241716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252125</v>
+        <v>121252127</v>
       </c>
       <c r="B4" t="n">
-        <v>78346</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,25 +887,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781581</v>
+        <v>781534</v>
       </c>
       <c r="R4" t="n">
-        <v>7241728</v>
+        <v>7241880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252124</v>
+        <v>121252129</v>
       </c>
       <c r="B5" t="n">
-        <v>89769</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -989,25 +989,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781534</v>
+        <v>781569</v>
       </c>
       <c r="R5" t="n">
-        <v>7241742</v>
+        <v>7241747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252126</v>
+        <v>121252124</v>
       </c>
       <c r="B6" t="n">
-        <v>92031</v>
+        <v>89769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R6" t="n">
-        <v>7241938</v>
+        <v>7241742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1182,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252129</v>
+        <v>121252125</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>78346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1194,25 +1193,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781569</v>
+        <v>781581</v>
       </c>
       <c r="R7" t="n">
-        <v>7241747</v>
+        <v>7241728</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252127</v>
+        <v>121252126</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>92031</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1296,25 +1295,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781534</v>
+        <v>781593</v>
       </c>
       <c r="R8" t="n">
-        <v>7241880</v>
+        <v>7241938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252123</v>
+        <v>121252128</v>
       </c>
       <c r="B9" t="n">
-        <v>90646</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781648</v>
+        <v>781534</v>
       </c>
       <c r="R9" t="n">
-        <v>7241716</v>
+        <v>7241742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252123</v>
+        <v>121252127</v>
       </c>
       <c r="B2" t="n">
-        <v>90646</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781648</v>
+        <v>781534</v>
       </c>
       <c r="R2" t="n">
-        <v>7241716</v>
+        <v>7241880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252127</v>
+        <v>121252128</v>
       </c>
       <c r="B4" t="n">
         <v>91996</v>
@@ -918,7 +918,7 @@
         <v>781534</v>
       </c>
       <c r="R4" t="n">
-        <v>7241880</v>
+        <v>7241742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252124</v>
+        <v>121252126</v>
       </c>
       <c r="B6" t="n">
-        <v>89769</v>
+        <v>92031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781534</v>
+        <v>781593</v>
       </c>
       <c r="R6" t="n">
-        <v>7241742</v>
+        <v>7241938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,6 +1163,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1181,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252125</v>
+        <v>121252123</v>
       </c>
       <c r="B7" t="n">
-        <v>78346</v>
+        <v>90646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781581</v>
+        <v>781648</v>
       </c>
       <c r="R7" t="n">
-        <v>7241728</v>
+        <v>7241716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252126</v>
+        <v>121252125</v>
       </c>
       <c r="B8" t="n">
-        <v>92031</v>
+        <v>78346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781593</v>
+        <v>781581</v>
       </c>
       <c r="R8" t="n">
-        <v>7241938</v>
+        <v>7241728</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252128</v>
+        <v>121252124</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>89769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252127</v>
+        <v>121252123</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>90646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781534</v>
+        <v>781648</v>
       </c>
       <c r="R2" t="n">
-        <v>7241880</v>
+        <v>7241716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252130</v>
+        <v>121252126</v>
       </c>
       <c r="B3" t="n">
-        <v>91411</v>
+        <v>92031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>757</v>
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781562</v>
+        <v>781593</v>
       </c>
       <c r="R3" t="n">
-        <v>7241723</v>
+        <v>7241938</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252128</v>
+        <v>121252124</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>89769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,25 +892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,7 +982,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252129</v>
+        <v>121252128</v>
       </c>
       <c r="B5" t="n">
         <v>91996</v>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781569</v>
+        <v>781534</v>
       </c>
       <c r="R5" t="n">
-        <v>7241747</v>
+        <v>7241742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252126</v>
+        <v>121252127</v>
       </c>
       <c r="B6" t="n">
-        <v>92031</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1091,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R6" t="n">
-        <v>7241938</v>
+        <v>7241880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1168,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1182,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252123</v>
+        <v>121252130</v>
       </c>
       <c r="B7" t="n">
-        <v>90646</v>
+        <v>91411</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,21 +1202,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781648</v>
+        <v>781562</v>
       </c>
       <c r="R7" t="n">
-        <v>7241716</v>
+        <v>7241723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1265,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252124</v>
+        <v>121252129</v>
       </c>
       <c r="B9" t="n">
-        <v>89769</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1398,25 +1398,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781534</v>
+        <v>781569</v>
       </c>
       <c r="R9" t="n">
-        <v>7241742</v>
+        <v>7241747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252123</v>
+        <v>121252130</v>
       </c>
       <c r="B2" t="n">
-        <v>90646</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781648</v>
+        <v>781562</v>
       </c>
       <c r="R2" t="n">
-        <v>7241716</v>
+        <v>7241723</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252126</v>
+        <v>121252124</v>
       </c>
       <c r="B3" t="n">
-        <v>92031</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781593</v>
+        <v>781534</v>
       </c>
       <c r="R3" t="n">
-        <v>7241938</v>
+        <v>7241742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +852,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252124</v>
+        <v>121252123</v>
       </c>
       <c r="B4" t="n">
-        <v>89769</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781534</v>
+        <v>781648</v>
       </c>
       <c r="R4" t="n">
-        <v>7241742</v>
+        <v>7241716</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +967,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252128</v>
+        <v>121252127</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1025,7 +1005,7 @@
         <v>781534</v>
       </c>
       <c r="R5" t="n">
-        <v>7241742</v>
+        <v>7241880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1064,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252127</v>
+        <v>121252128</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1127,7 +1102,7 @@
         <v>781534</v>
       </c>
       <c r="R6" t="n">
-        <v>7241880</v>
+        <v>7241742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,15 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252130</v>
+        <v>121252129</v>
       </c>
       <c r="B7" t="n">
-        <v>91411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,16 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>757</v>
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781562</v>
+        <v>781569</v>
       </c>
       <c r="R7" t="n">
-        <v>7241723</v>
+        <v>7241747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1240,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1284,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252125</v>
+        <v>121252126</v>
       </c>
       <c r="B8" t="n">
-        <v>78346</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781581</v>
+        <v>781593</v>
       </c>
       <c r="R8" t="n">
-        <v>7241728</v>
+        <v>7241938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1337,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,37 +1356,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252129</v>
+        <v>121252125</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781569</v>
+        <v>781581</v>
       </c>
       <c r="R9" t="n">
-        <v>7241747</v>
+        <v>7241728</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 2801-2024 artfynd.xlsx
+++ b/artfynd/A 2801-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252128</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252129</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252126</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1450,8 +1490,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>